--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486304_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486304_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. VILA SOLEY</t>
+          <t>G. JOFRESA SARRET</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3988</v>
+        <v>4.2703</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0998</v>
+        <v>3.5015</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2991</v>
+        <v>0.7688</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0576</v>
+        <v>1.7931</v>
       </c>
       <c r="H2" t="n">
-        <v>2.3453</v>
+        <v>-0.0851</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2877</v>
+        <v>1.8782</v>
       </c>
       <c r="J2" t="n">
-        <v>3.0259</v>
+        <v>2.8754</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9111</v>
+        <v>1.2108</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1147</v>
+        <v>1.6647</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.9683</v>
+        <v>-1.0823</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5659</v>
+        <v>-1.2959</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4024</v>
+        <v>0.2136</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.9576</v>
+        <v>1.5225</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2367</v>
+        <v>0.6979</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6187</v>
+        <v>0.6261</v>
       </c>
       <c r="U2" t="n">
-        <v>0.618</v>
+        <v>0.0718</v>
       </c>
       <c r="V2" t="n">
-        <v>0.452</v>
+        <v>0.2568</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3082</v>
+        <v>0.2568</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. JOFRESA SARRET</t>
+          <t>R. VILA SOLEY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8156</v>
+        <v>4.0492</v>
       </c>
       <c r="E3" t="n">
-        <v>2.831</v>
+        <v>3.2742</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9846</v>
+        <v>0.7751</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7931</v>
+        <v>2.0576</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0851</v>
+        <v>2.3453</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8782</v>
+        <v>-0.2877</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8754</v>
+        <v>3.0259</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2108</v>
+        <v>2.9111</v>
       </c>
       <c r="L3" t="n">
-        <v>1.6647</v>
+        <v>0.1147</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0823</v>
+        <v>-0.9683</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.2959</v>
+        <v>-0.5659</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2136</v>
+        <v>-0.4024</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5225</v>
+        <v>1.9576</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2431</v>
+        <v>0.8872</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0445</v>
+        <v>0.7931</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2876</v>
+        <v>0.094</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2568</v>
+        <v>0.452</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2568</v>
+        <v>-0.3082</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0511</v>
+        <v>3.7045</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5041</v>
+        <v>1.3116</v>
       </c>
       <c r="F4" t="n">
-        <v>2.547</v>
+        <v>2.3929</v>
       </c>
       <c r="G4" t="n">
         <v>3.1708</v>
@@ -766,13 +766,13 @@
         <v>3.0451</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2073</v>
+        <v>0.4461</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2824</v>
+        <v>0.5252</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0751</v>
+        <v>-0.079</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5649999999999999</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2885</v>
+        <v>2.5033</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2891</v>
+        <v>1.1341</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9994</v>
+        <v>1.3692</v>
       </c>
       <c r="G5" t="n">
         <v>2.5386</v>
@@ -844,13 +844,13 @@
         <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1456</v>
+        <v>0.3605</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9421</v>
+        <v>0.7871</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7965</v>
+        <v>-0.4266</v>
       </c>
       <c r="V5" t="n">
         <v>0.2568</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ALONSO CUEVAS</t>
+          <t>G. GIL GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1231</v>
+        <v>1.4171</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0732</v>
+        <v>-0.8964</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0499</v>
+        <v>2.3135</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.9068</v>
+        <v>-0.7444</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0121</v>
+        <v>-0.9978</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.9188</v>
+        <v>0.2534</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.191</v>
+        <v>-0.5203</v>
       </c>
       <c r="K6" t="n">
-        <v>1.241</v>
+        <v>-0.1976</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.4319</v>
+        <v>-0.3227</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7158</v>
+        <v>-0.2241</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2289</v>
+        <v>-0.8003</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4869</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9576</v>
+        <v>2.3926</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2898</v>
+        <v>0.5296</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4817</v>
+        <v>0.9288999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1919</v>
+        <v>-0.3993</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.5443</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.5443</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. GIL GARCIA</t>
+          <t>A. ALONSO CUEVAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0142</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1451</v>
+        <v>0.5397</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1593</v>
+        <v>0.1423</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7444</v>
+        <v>-1.9068</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9978</v>
+        <v>0.0121</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2534</v>
+        <v>-1.9188</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5203</v>
+        <v>-0.191</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1976</v>
+        <v>1.241</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.3227</v>
+        <v>-1.4319</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2241</v>
+        <v>-1.7158</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8003</v>
+        <v>-1.2289</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5760999999999999</v>
+        <v>-0.4869</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3926</v>
+        <v>1.9576</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1268</v>
+        <v>0.8487</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6802</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5534</v>
+        <v>-0.0994</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5443</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5443</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. BROWN-FERGUSON</t>
+          <t>F. TERINS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8373</v>
+        <v>0.505</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2185</v>
+        <v>-0.3576</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3812</v>
+        <v>0.8626</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3826</v>
+        <v>-0.4639</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3746</v>
+        <v>1.1951</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.008</v>
+        <v>-1.6591</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5011</v>
+        <v>-1.0886</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5776</v>
+        <v>0.4015</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0765</v>
+        <v>-1.4901</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8814</v>
+        <v>0.6247</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7969000000000001</v>
+        <v>0.7936</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.1689</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6525</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="S8" t="n">
-        <v>2.1323</v>
+        <v>0.4915</v>
       </c>
       <c r="T8" t="n">
-        <v>1.7196</v>
+        <v>0.6886</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4127</v>
+        <v>-0.1971</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5649999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6704</v>
+        <v>0.1608</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9102</v>
+        <v>1.3081</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2397</v>
+        <v>-1.1473</v>
       </c>
       <c r="G9" t="n">
         <v>-1.4138</v>
@@ -1156,13 +1156,13 @@
         <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7622</v>
+        <v>0.2527</v>
       </c>
       <c r="T9" t="n">
-        <v>1.4456</v>
+        <v>0.8436</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6834</v>
+        <v>-0.5909</v>
       </c>
       <c r="V9" t="n">
         <v>0.452</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. TERINS</t>
+          <t>J. BROWN-FERGUSON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5809</v>
+        <v>0.0935</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3202</v>
+        <v>0.6597</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7393</v>
+        <v>-0.5662</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4639</v>
+        <v>-1.3826</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1951</v>
+        <v>-1.3746</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.6591</v>
+        <v>-0.008</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0886</v>
+        <v>-0.5011</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4015</v>
+        <v>-0.5776</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4901</v>
+        <v>0.0765</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6247</v>
+        <v>-0.8814</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7936</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1689</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6525</v>
+        <v>0.6525</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5944</v>
+        <v>1.3886</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.274</v>
+        <v>1.1608</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3204</v>
+        <v>0.2277</v>
       </c>
       <c r="V10" t="n">
-        <v>1.13</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. PARRADO CALABRIA</t>
+          <t>A. ALONSO RUIZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7715</v>
+        <v>-1.0034</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9111</v>
+        <v>-0.2013</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1396</v>
+        <v>-0.8021</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3504</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.1482</v>
+        <v>-0.6264999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>2.7978</v>
+        <v>0.6183</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0617</v>
+        <v>1.1626</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.9009</v>
+        <v>-0.1762</v>
       </c>
       <c r="L11" t="n">
-        <v>1.8392</v>
+        <v>1.3387</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2887</v>
+        <v>-1.1707</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2473</v>
+        <v>-0.4504</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9586</v>
+        <v>-0.7204</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.0875</v>
+        <v>-0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.2626</v>
+        <v>-2.3926</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1751</v>
+        <v>2.3926</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4267</v>
+        <v>0.6997</v>
       </c>
       <c r="T11" t="n">
-        <v>1.4132</v>
+        <v>1.0287</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0134</v>
+        <v>-0.329</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.7602</v>
+        <v>-1.695</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.7602</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. ALONSO RUIZ</t>
+          <t>A. PARRADO CALABRIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.15</v>
+        <v>-2.5516</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0089</v>
+        <v>-3.4446</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1411</v>
+        <v>0.893</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.008200000000000001</v>
+        <v>-1.3504</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6264999999999999</v>
+        <v>-4.1482</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6183</v>
+        <v>2.7978</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1626</v>
+        <v>-1.0617</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1762</v>
+        <v>-2.9009</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3387</v>
+        <v>1.8392</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1707</v>
+        <v>-0.2887</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4504</v>
+        <v>-1.2473</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7204</v>
+        <v>0.9586</v>
       </c>
       <c r="P12" t="n">
-        <v>-0</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.3926</v>
+        <v>-3.2626</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3926</v>
+        <v>2.1751</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4469</v>
+        <v>0.6465</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2211</v>
+        <v>0.8797</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.668</v>
+        <v>-0.2331</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.695</v>
+        <v>-0.7602</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.695</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.7232</v>
+        <v>-2.83</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.935</v>
+        <v>-2.196</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7882</v>
+        <v>-0.634</v>
       </c>
       <c r="G13" t="n">
         <v>-3.8359</v>
@@ -1468,13 +1468,13 @@
         <v>0.6525</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4693</v>
+        <v>0.4239</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.125</v>
+        <v>0.6141</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3443</v>
+        <v>-0.1902</v>
       </c>
       <c r="V13" t="n">
         <v>1.017</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.973399999999998</v>
+        <v>11.0007</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6056</v>
+        <v>4.633000000000003</v>
       </c>
       <c r="F14" t="n">
-        <v>6.368</v>
+        <v>6.367799999999999</v>
       </c>
       <c r="G14" t="n">
         <v>-1.5459</v>
@@ -1525,16 +1525,16 @@
         <v>7.1655</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.3463999999999998</v>
+        <v>-0.3463999999999996</v>
       </c>
       <c r="M14" t="n">
         <v>-8.364800000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-9.233400000000003</v>
+        <v>-9.233400000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8684999999999993</v>
+        <v>0.8684999999999995</v>
       </c>
       <c r="P14" t="n">
         <v>4.3501</v>
@@ -1546,16 +1546,16 @@
         <v>19.5756</v>
       </c>
       <c r="S14" t="n">
-        <v>6.6453</v>
+        <v>7.672899999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>8.7963</v>
+        <v>9.824000000000002</v>
       </c>
       <c r="U14" t="n">
         <v>-2.1511</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5236999999999998</v>
+        <v>0.5236999999999994</v>
       </c>
       <c r="W14" t="n">
         <v>3.2154</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0252</v>
+        <v>2.4176</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2351</v>
+        <v>2.4528</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2099</v>
+        <v>-0.0352</v>
       </c>
       <c r="G15" t="n">
         <v>3.4701</v>
@@ -1624,13 +1624,13 @@
         <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1423</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9167</v>
+        <v>1.1344</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7744</v>
+        <v>-0.5997</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9347</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9036</v>
+        <v>2.393</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0867</v>
+        <v>0.4219</v>
       </c>
       <c r="F16" t="n">
-        <v>1.817</v>
+        <v>1.9711</v>
       </c>
       <c r="G16" t="n">
         <v>1.8249</v>
@@ -1702,13 +1702,13 @@
         <v>1.7401</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.6613</v>
+        <v>-1.172</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3869</v>
+        <v>-0.0517</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.2744</v>
+        <v>-1.1203</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. ANSORREGUI DEBA</t>
+          <t>I. ARROYO VARELA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.687</v>
+        <v>2.0917</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0023</v>
+        <v>3.2945</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3152</v>
+        <v>-1.2028</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.6953</v>
+        <v>3.2376</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8179</v>
+        <v>2.4846</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8774</v>
+        <v>0.753</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4573</v>
+        <v>4.1782</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3808</v>
+        <v>3.8324</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0765</v>
+        <v>0.3459</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.1526</v>
+        <v>-0.9406</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1987</v>
+        <v>-1.3477</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9539</v>
+        <v>0.4072</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7401</v>
+        <v>-0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.435</v>
+        <v>-1.5225</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1751</v>
+        <v>1.5225</v>
       </c>
       <c r="S17" t="n">
-        <v>0.882</v>
+        <v>-1.7109</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2197</v>
+        <v>-0.1214</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3377</v>
+        <v>-1.5896</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7602</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W17" t="n">
         <v>0.7602</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6585</v>
+        <v>2.0053</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0253</v>
+        <v>0.2488</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6332</v>
+        <v>1.7564</v>
       </c>
       <c r="G18" t="n">
         <v>1.5839</v>
@@ -1858,13 +1858,13 @@
         <v>1.5225</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4454</v>
+        <v>-0.0985</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1935</v>
+        <v>0.03</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2519</v>
+        <v>-0.1286</v>
       </c>
       <c r="V18" t="n">
         <v>2.2599</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. ARROYO VARELA</t>
+          <t>G. MAIZA APECECHEA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6839</v>
+        <v>1.5499</v>
       </c>
       <c r="E19" t="n">
-        <v>2.4005</v>
+        <v>2.2473</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7166</v>
+        <v>-0.6974</v>
       </c>
       <c r="G19" t="n">
-        <v>3.2376</v>
+        <v>1.5549</v>
       </c>
       <c r="H19" t="n">
-        <v>2.4846</v>
+        <v>-1.5999</v>
       </c>
       <c r="I19" t="n">
-        <v>0.753</v>
+        <v>3.1548</v>
       </c>
       <c r="J19" t="n">
-        <v>4.1782</v>
+        <v>2.5416</v>
       </c>
       <c r="K19" t="n">
-        <v>3.8324</v>
+        <v>-0.2706</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3459</v>
+        <v>2.8121</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9406</v>
+        <v>-0.9867</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3477</v>
+        <v>-1.3293</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4072</v>
+        <v>0.3426</v>
       </c>
       <c r="P19" t="n">
-        <v>-0</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.5225</v>
+        <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>-3.1188</v>
+        <v>-0.3524</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0154</v>
+        <v>0.2283</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.1033</v>
+        <v>-0.5807</v>
       </c>
       <c r="V19" t="n">
         <v>0.5649999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>0.7602</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. MAIZA APECECHEA</t>
+          <t>M. ANSORREGUI DEBA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6623</v>
+        <v>0.373</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6886</v>
+        <v>0.9964</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0263</v>
+        <v>-0.6234</v>
       </c>
       <c r="G20" t="n">
-        <v>1.5549</v>
+        <v>-1.6953</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5999</v>
+        <v>-0.8179</v>
       </c>
       <c r="I20" t="n">
-        <v>3.1548</v>
+        <v>-0.8774</v>
       </c>
       <c r="J20" t="n">
-        <v>2.5416</v>
+        <v>0.4573</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2706</v>
+        <v>0.3808</v>
       </c>
       <c r="L20" t="n">
-        <v>2.8121</v>
+        <v>0.0765</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9867</v>
+        <v>-2.1526</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3293</v>
+        <v>-1.1987</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3426</v>
+        <v>-0.9539</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2175</v>
+        <v>1.7401</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0875</v>
+        <v>-0.435</v>
       </c>
       <c r="R20" t="n">
-        <v>0.87</v>
+        <v>2.1751</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.24</v>
+        <v>-0.432</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3305</v>
+        <v>0.2139</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9096</v>
+        <v>-0.6459</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.7602</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.7602</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0788</v>
+        <v>-0.3682</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6263</v>
+        <v>0.1793</v>
       </c>
       <c r="F21" t="n">
         <v>-0.5475</v>
@@ -2092,10 +2092,10 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6766</v>
+        <v>0.2295</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6081</v>
+        <v>0.161</v>
       </c>
       <c r="U21" t="n">
         <v>0.06850000000000001</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2919</v>
+        <v>-1.3484</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6287</v>
+        <v>0.1817</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9206</v>
+        <v>-1.5301</v>
       </c>
       <c r="G22" t="n">
         <v>0.0429</v>
@@ -2170,13 +2170,13 @@
         <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7947</v>
+        <v>0.7381</v>
       </c>
       <c r="T22" t="n">
-        <v>1.4336</v>
+        <v>0.9866</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6389</v>
+        <v>-0.2485</v>
       </c>
       <c r="V22" t="n">
         <v>-2.9995</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L. TERRY</t>
+          <t>T. MCGHIE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9135</v>
+        <v>-3.975</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3557</v>
+        <v>-4.4403</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5578</v>
+        <v>0.4653</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.9097</v>
+        <v>-1.4506</v>
       </c>
       <c r="H23" t="n">
-        <v>1.5605</v>
+        <v>-0.5262</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.4703</v>
+        <v>-0.9243</v>
       </c>
       <c r="J23" t="n">
-        <v>0.112</v>
+        <v>-1.3628</v>
       </c>
       <c r="K23" t="n">
-        <v>1.5639</v>
+        <v>0.2222</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.4519</v>
+        <v>-1.5849</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0217</v>
+        <v>-0.0878</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0033</v>
+        <v>-0.7484</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0184</v>
+        <v>0.6606</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.1751</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.6976</v>
+        <v>-3.2626</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4589</v>
+        <v>-0.1319</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5997</v>
+        <v>0.1851</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0586</v>
+        <v>-0.317</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3698</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3698</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. NICOLAU ALEDON</t>
+          <t>L. TERRY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.2549</v>
+        <v>-4.3297</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.094</v>
+        <v>-3.8027</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8391</v>
+        <v>-0.5269</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7268</v>
+        <v>-0.9097</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.0615</v>
+        <v>1.5605</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3347</v>
+        <v>-2.4703</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.1362</v>
+        <v>0.112</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.2127</v>
+        <v>1.5639</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0765</v>
+        <v>-1.4519</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5907</v>
+        <v>-1.0217</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8488</v>
+        <v>-0.0033</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2582</v>
+        <v>-1.0184</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.7401</v>
+        <v>-2.1751</v>
       </c>
       <c r="Q24" t="n">
         <v>-3.6976</v>
       </c>
       <c r="R24" t="n">
-        <v>1.9576</v>
+        <v>1.5225</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4183</v>
+        <v>-0.8751</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8904</v>
+        <v>0.1526</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5278</v>
+        <v>-1.0278</v>
       </c>
       <c r="V24" t="n">
         <v>-0.3698</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>T. MCGHIE</t>
+          <t>J. NICOLAU ALEDON</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,64 +2359,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.7868</v>
+        <v>-4.4013</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.8873</v>
+        <v>-4.8705</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1005</v>
+        <v>0.4692</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.4506</v>
+        <v>-0.7268</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.5262</v>
+        <v>-1.0615</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.9243</v>
+        <v>0.3347</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.3628</v>
+        <v>-0.1362</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2222</v>
+        <v>-0.2127</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.5849</v>
+        <v>0.0765</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0878</v>
+        <v>-0.5907</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.7484</v>
+        <v>-0.8488</v>
       </c>
       <c r="O25" t="n">
-        <v>0.6606</v>
+        <v>0.2582</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.3926</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.2626</v>
+        <v>-3.6976</v>
       </c>
       <c r="R25" t="n">
-        <v>0.87</v>
+        <v>1.9576</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9437</v>
+        <v>-1.5646</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.262</v>
+        <v>-0.6669</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6817</v>
+        <v>-0.8977000000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.4257</v>
+        <v>-4.8913</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.7242</v>
+        <v>-3.2772</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.7014</v>
+        <v>-1.6141</v>
       </c>
       <c r="G26" t="n">
         <v>-4.7885</v>
@@ -2482,13 +2482,13 @@
         <v>0.6525</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.8546</v>
+        <v>-0.3203</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.548</v>
+        <v>-0.1009</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3067</v>
+        <v>-0.2193</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,22 +2515,22 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-9.9735</v>
+        <v>-8.4834</v>
       </c>
       <c r="E27" t="n">
-        <v>-6.367700000000001</v>
+        <v>-6.367999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.6055</v>
+        <v>-2.1154</v>
       </c>
       <c r="G27" t="n">
-        <v>1.545700000000002</v>
+        <v>1.545700000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>2.067700000000001</v>
+        <v>2.0677</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.5220000000000002</v>
+        <v>-0.522</v>
       </c>
       <c r="J27" t="n">
         <v>8.364699999999999</v>
@@ -2542,13 +2542,13 @@
         <v>-0.8684000000000003</v>
       </c>
       <c r="M27" t="n">
-        <v>-6.819199999999999</v>
+        <v>-6.8192</v>
       </c>
       <c r="N27" t="n">
         <v>-7.1655</v>
       </c>
       <c r="O27" t="n">
-        <v>0.3463999999999996</v>
+        <v>0.3463999999999997</v>
       </c>
       <c r="P27" t="n">
         <v>-4.3502</v>
@@ -2560,16 +2560,16 @@
         <v>15.2253</v>
       </c>
       <c r="S27" t="n">
-        <v>-6.645399999999999</v>
+        <v>-5.155299999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>2.1511</v>
+        <v>2.150999999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>-8.7965</v>
+        <v>-7.3066</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.5236999999999996</v>
+        <v>-0.5236999999999998</v>
       </c>
       <c r="W27" t="n">
         <v>2.6917</v>
